--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260910.xlsx
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>113,722,628</t>
+          <t>17,514,764</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>17,514,764</t>
+          <t>113,722,628</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
